--- a/data/VACA PANCHI CAROLINA.xlsx
+++ b/data/VACA PANCHI CAROLINA.xlsx
@@ -1685,13 +1685,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1736,17 +1736,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OTROS</t>
+          <t>240X80 PORCELANATO</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>0</v>
+        <v>2600</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>-10.44</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.44</v>
+        <v>2600</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>0</v>
@@ -1760,39 +1760,207 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>FREGADEROS DE COCINA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VACA PANCHI CAROLINA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GRIFERIAS</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>172.82</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>172.82</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VACA PANCHI CAROLINA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INODOROS</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VACA PANCHI CAROLINA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LAVABOS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VACA PANCHI CAROLINA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VACA PANCHI CAROLINA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PANELES DECORATIVOS</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>203.76</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>203.76</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VACA PANCHI CAROLINA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>PORCELANATO</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="7" t="inlineStr">
+      <c r="C9" s="2" t="n">
+        <v>20250.92</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>20250.92</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VACA PANCHI CAROLINA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAL SOLUBLE</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>-10.44</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>20010.44</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>-0.000522</v>
+      <c r="C11" s="2" t="n">
+        <v>24907</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>24907</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/VACA PANCHI CAROLINA.xlsx
+++ b/data/VACA PANCHI CAROLINA.xlsx
@@ -1685,7 +1685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1904,17 +1904,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PORCELANATO</t>
+          <t>PANELES PVC Y PU</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>20250.92</v>
+        <v>115</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>20250.92</v>
+        <v>115</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>0</v>
@@ -1928,38 +1928,62 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>PORCELANATO</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>20250.92</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>20250.92</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VACA PANCHI CAROLINA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>SAL SOLUBLE</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C11" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="n">
+      <c r="D11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="F11" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>24907</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>24907</v>
-      </c>
-      <c r="F11" s="3" t="n">
+      <c r="C12" s="2" t="n">
+        <v>25022</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>25022</v>
+      </c>
+      <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
     </row>
